--- a/entrega/checklist-cliente.xlsx
+++ b/entrega/checklist-cliente.xlsx
@@ -50,9 +50,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,8 +421,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -454,332 +464,362 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Consentimiento</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Se informa a estudiantes/docentes la finalidad del uso de sus horarios y correos para la logística de la encuesta.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>🔍 Por verificar</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Pendiente confirmar con el cliente.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Incluir aviso de tratamiento específico en la comunicación de citación (Ley 1581 de 2012, Art. 4 y 9).</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ Parcial</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>La Política de Tratamiento de Datos Personales de la Universidad (vigente desde 2013, Num. 4-a y Num. 7) obliga a informar la finalidad antes o al momento de recolectar el dato, pero no se encontró evidencia de que el mensaje de notificación del flujo de Power Automate (Cruce de Horarios / Notificación a Profesores) incluya un aviso de privacidad específico de este proceso.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Incluir en el cuerpo del correo/notificación un aviso de privacidad breve citando la finalidad puntual (programación y aplicación de la encuesta de satisfacción) y el fundamento legal (Ley 1581 de 2012, Política institucional).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Consentimiento</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Existe canal visible para que estudiantes/docentes consulten o se opongan al uso de sus datos en este proceso.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>🔍 Por verificar</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Pendiente confirmar con el cliente.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Referenciar protecciondedatos@unisabana.edu.co en la comunicación, conforme a la Política de Tratamiento de Datos Personales.</t>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ Parcial</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>La política institucional define un procedimiento formal de PQR (Num. 10, plazo máximo 15 días hábiles), pero no se evidenció que la comunicación enviada a estudiantes/profesores en este proceso referencie explícitamente ese canal.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Agregar al pie de la notificación el canal institucional de PQR de datos personales y el enlace a la política vigente.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Protección de Datos (Horarios)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>El cruce/consolidación de horarios de estudiantes respeta el principio de finalidad y no se reutiliza para otros fines.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>🔍 Por verificar</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Pendiente confirmar con el cliente.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Documentar la finalidad del tratamiento en un anexo del proceso.</t>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ Parcial</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>El principio de finalidad (Num. 4-a de la política) prohíbe reutilizar el dato para fines distintos a los informados, pero no se confirmó con el cliente si los horarios cruzados desde SIGA se usan únicamente para la encuesta o si se reutilizan en otros reportes (p. ej. Power BI institucional).</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Documentar explícitamente en el flujo (o en un anexo del proceso) que los horarios cruzados se usan únicamente para la programación de la encuesta, y verificar que no exista reutilización en otros tableros.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Protección de Datos (Horarios)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>El acceso a los horarios está restringido a los roles que administran la logística de la encuesta.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>🔍 Por verificar</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Pendiente confirmar con el cliente.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Definir matriz de roles y permisos en el flujo de Power Automate/SharePoint.</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ Parcial</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>No se tuvo acceso a la configuración real de permisos del sitio de SharePoint que aloja el Repositorio de Programación; este mismo hallazgo quedó documentado como riesgo Alto (T1) en el análisis STRIDE del Taller 5.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Definir y documentar una matriz de roles y permisos (RBAC) en SharePoint/Power Platform limitada al equipo de Automatización y al Coordinador de Encuestas.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Correos Institucionales</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>El envío de notificaciones obligatorias a profesores usa el correo institucional autenticado y queda trazado.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>🔍 Por verificar</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Pendiente confirmar con el cliente.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Confirmar que Power Automate use la cuenta institucional (no personal) y registre el envío (Ley 1273 de 2009).</t>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>✅ Cumple</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Power Automate exige autenticación OAuth con la cuenta de conexión institucional del conector de Office 365 Outlook / Exchange Online; no admite envío anónimo ni cuentas externas sin autorización del tenant. Además, cada ejecución del flujo de notificación queda registrada automáticamente en el historial de ejecuciones (Run History) de Power Automate, con fecha, estado y detalle de cada paso — trazabilidad nativa de la plataforma, sin configuración adicional.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Exportar periódicamente el historial de ejecuciones a un registro de auditoría de largo plazo, ya que Power Automate conserva el historial de ejecuciones solo por un periodo limitado por defecto.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Correos Institucionales</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Existe un reglamento o política publicada sobre el uso adecuado del correo institucional.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>🔍 Por verificar</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>No se halló documento público (ver entrega/referencias.md).</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Si no existe internamente, señalar como brecha documental y recomendar su creación.</t>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ Parcial</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>No se encontró un reglamento o política institucional publicada específicamente sobre el uso adecuado del correo institucional (ver entrega/referencias.md).</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Si el documento no existe internamente, registrar como brecha documental y recomendar su creación, o referenciar el apartado correspondiente del Código de Ética y Buen Gobierno si lo cubre.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Seguridad (ISO 27001 / M365)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>La automatización usa exclusivamente herramientas ya autorizadas por la Universidad (O365, Power Automate, Power BI) con controles del proveedor.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>🔍 Por verificar</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Pendiente confirmar con el cliente.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Verificar configuración de DLP y permisos en el tenant M365 institucional.</t>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>✅ Cumple</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>La restricción explícita del cliente (Ficha de Caracterización, Taller 0) exige que la automatización use únicamente herramientas ya autorizadas por la Universidad (Office 365, Power Automate, Power BI). Además, la política de datos personales (Num. 6-C) permite subcontratar el tratamiento a un "Encargado" externo (en este caso, Microsoft) siempre que se exijan medidas de seguridad apropiadas — condición que Microsoft 365 cubre mediante su marco contractual de cumplimiento (Data Protection Addendum / Microsoft Trust Center).</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Verificar y documentar que exista (o se suscriba) la cláusula o contrato de transmisión de datos personales con Microsoft exigido por el artículo 25 del Decreto 1377 de 2013 para encargados del tratamiento.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Seguridad (ISO 27001)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Existen logs de auditoría de quién accede/modifica horarios y resultados de la encuesta.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>🔍 Por verificar</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Pendiente confirmar con el cliente.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Habilitar auditoría nativa de Microsoft 365 / Power Automate.</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ Parcial</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft 365 ofrece de forma nativa un registro de auditoría unificado (Microsoft Purview Audit) que puede capturar accesos y cambios en SharePoint, pero no se confirmó con el cliente si está habilitado, con qué periodo de retención, ni si cubre específicamente las listas del Repositorio de Programación.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar con el área de TI institucional la activación del registro de auditoría de Microsoft Purview sobre el sitio de SharePoint del proceso, con una política de retención de al menos 1 año.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Retención</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Existe política de retención y eliminación de horarios y respuestas de la encuesta una vez cumplida su finalidad.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>🔍 Por verificar</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Pendiente confirmar con el cliente.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Definir tiempos de conservación acordes a la Política de Datos Personales.</t>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ Parcial</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>La política institucional (Num. 9) exige suprimir los datos personales una vez cumplida su finalidad, salvo obligación legal, pero no define plazos concretos para este proceso ni se confirmó que exista una regla de retención/eliminación automática configurada en SharePoint o Power Platform para los horarios y respuestas de la encuesta.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Definir un plazo concreto de conservación (p. ej. hasta el cierre del periodo de acreditación correspondiente) y configurar una política de retención/eliminación automática en Microsoft Purview sobre las listas de SharePoint del proceso.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Registro de Bases de Datos</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>La base generada por el proceso (horarios + respuestas) está incluida en el Registro Nacional de Bases de Datos (RNBD) de la Universidad, si aplica.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>🔍 Por verificar</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Pendiente confirmar con el cliente.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Verificar inclusión en el RNBD institucional (Decreto 886 de 2014).</t>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ Parcial</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>El documento de política de tratamiento de datos disponible públicamente (vigente desde 2013) no menciona el Registro Nacional de Bases de Datos (RNBD, Decreto 886 de 2014, posterior a esa versión del documento); no se confirmó con el cliente si la base generada por este proceso (u otra base instituticional que la contenga) está inscrita en el RNBD de la Superintendencia de Industria y Comercio.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Verificar con la Dirección General Administrativa (área responsable general del tratamiento según la política) si la base de datos del proceso está cubierta por el registro RNBD institucional vigente.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Roles y Responsabilidades</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Estudiantes/docentes conocen el canal institucional para ejercer derechos ARCO sobre sus datos en este proceso.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>🔍 Por verificar</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Pendiente confirmar con el cliente.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Referenciar el canal en la comunicación, conforme al Reglamento de Estudiantes.</t>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ Parcial</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>La política institucional define el procedimiento formal para ejercer los derechos de acceso, actualización, rectificación y supresión (Num. 5), pero no se evidenció que la comunicación del proceso de encuesta informe a estudiantes y profesores sobre este canal específico ni sobre qué área (Dirección de Registro Academico / Dirección de Desarrollo Humano, según la tabla de áreas encargadas de la política) es la responsable para este caso.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Referenciar en la notificación el procedimiento de PQR de la política institucional y aclarar cuál es el área encargada (Registro Académico para estudiantes, Desarrollo Humano para profesores) según la tabla de responsables de la política.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Aseguramiento de la Calidad (CNA)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>La información generada por el proceso (participación, resultados de la encuesta) se consolida con trazabilidad y calidad suficientes para soportar los procesos de autoevaluación y acreditación institucional.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ Parcial</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>El Acuerdo 01 de 2025 del CESU (Lineamientos CNA, Factor 4 – Sistema Interno de Aseguramiento de la Calidad, Característica 13) exige que la institución consolide información veraz y actualizada para sus procesos de autoevaluación, y el propio informe del Taller 5 (Seguridad) señala que esta encuesta es insumo directo del proceso de acreditación institucional. Dado que el almacén actual (SharePoint Lists / Excel) aún no tiene confirmados los controles de acceso, auditoría y retención de los ítems 4, 8 y 9 de este checklist, no se puede garantizar plenamente la integridad de esta información de cara a un proceso de acreditación.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Cerrar primero las brechas de control de acceso, auditoría y retención (ítems 4, 8 y 9); una vez cerradas, documentar explícitamente cómo los datos de esta encuesta alimentan el Sistema Interno de Aseguramiento de la Calidad para el próximo ciclo de autoevaluación CNA.</t>
         </is>
       </c>
     </row>
@@ -794,8 +834,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -821,6 +868,276 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Nivel de Prioridad</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consentimiento</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>No se evidencia aviso de privacidad específico del proceso en la notificación a estudiantes/profesores.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Incluir aviso de privacidad breve con la finalidad puntual del tratamiento en la notificación del flujo.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Consentimiento</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>No se referencia el canal institucional de PQR de datos personales en la comunicación del proceso.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Agregar el canal de PQR y enlace a la política vigente al pie de la notificación.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Protección de Datos (Horarios)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>No se confirmó que los horarios cruzados desde SIGA se usen únicamente para la encuesta y no se reutilicen en otros reportes.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Documentar explícitamente el alcance de uso de los horarios cruzados y verificar ausencia de reutilización.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Protección de Datos (Horarios)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>El acceso al Repositorio de Programación en SharePoint no tiene confirmada una matriz de roles y permisos restringida.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Definir y documentar una matriz de roles (RBAC) limitada al equipo de Automatización y al Coordinador de Encuestas.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Correos Institucionales</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>No existe reglamento o política publicada sobre el uso adecuado del correo institucional.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Registrar como brecha documental y recomendar su creación, o referenciar el Código de Ética y Buen Gobierno si aplica.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Seguridad (ISO 27001 / M365)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>No se confirmó la activación del registro de auditoría de Microsoft Purview sobre el sitio de SharePoint del proceso.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar con TI institucional la activación del log de auditoría con retención de al menos 1 año.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Retención</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>No existe política de retención/eliminación automática configurada para horarios y respuestas de la encuesta.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Definir plazo de conservación y configurar regla de retención en Microsoft Purview.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Registro de Bases de Datos</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>No se confirmó si la base del proceso está cubierta por el registro RNBD institucional vigente.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Verificar con la Dirección General Administrativa la cobertura del RNBD institucional sobre esta base.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Roles y Responsabilidades</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>La comunicación del proceso no informa el área responsable específica para ejercer derechos ARCO en este caso.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Referenciar en la notificación el área encargada (Registro Académico / Desarrollo Humano) según la política institucional.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Aseguramiento de la Calidad (CNA)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>La integridad y trazabilidad de los datos de la encuesta para el proceso de acreditación institucional no está garantizada mientras persistan las brechas de acceso, auditoría y retención.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Cerrar primero las brechas de acceso, auditoría y retención; luego documentar la trazabilidad de estos datos hacia el Sistema Interno de Aseguramiento de la Calidad.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
     </row>
